--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXIII/LTAIPT_A63F23C.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/3ER_TRIMESTRE/FRACCIONES XXI-XXX/FRACC XXIII/LTAIPT_A63F23C.xlsx
@@ -12,20 +12,22 @@
     <sheet name="Hidden_2" sheetId="3" r:id="rId3"/>
     <sheet name="Hidden_3" sheetId="4" r:id="rId4"/>
     <sheet name="Hidden_4" sheetId="5" r:id="rId5"/>
-    <sheet name="Tabla_468859" sheetId="6" r:id="rId6"/>
+    <sheet name="Hidden_5" sheetId="6" r:id="rId6"/>
+    <sheet name="Tabla_468859" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="Hidden_15">Hidden_1!$A$1:$A$3</definedName>
     <definedName name="Hidden_26">Hidden_2!$A$1:$A$10</definedName>
     <definedName name="Hidden_311">Hidden_3!$A$1:$A$4</definedName>
     <definedName name="Hidden_413">Hidden_4!$A$1:$A$3</definedName>
+    <definedName name="Hidden_514">Hidden_5!$A$1:$A$3</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="120">
   <si>
     <t>50878</t>
   </si>
@@ -105,6 +107,9 @@
     <t>468854</t>
   </si>
   <si>
+    <t>571963</t>
+  </si>
+  <si>
     <t>468855</t>
   </si>
   <si>
@@ -180,7 +185,7 @@
     <t>Descripción de unidad, por ejemplo: spot de 30 segundos (radio); mensaje en TV 20 segundos</t>
   </si>
   <si>
-    <t>Concepto o campaña</t>
+    <t>Concepto o campaña (Redactada con perspectiva de género)</t>
   </si>
   <si>
     <t>Clave única de identificación de campaña o aviso institucional, en su caso</t>
@@ -195,7 +200,10 @@
     <t>Ámbito geográfico de cobertura</t>
   </si>
   <si>
-    <t>Sexo (catálogo)</t>
+    <t>ESTE CRITERIO APLICA PARA EJERCICIOS ANTERIORES AL 01/04/2023 -&gt; Sexo (catálogo)</t>
+  </si>
+  <si>
+    <t>ESTE CRITERIO APLICA A PARTIR DEL 01/04/2023 -&gt; Sexo (catálogo)</t>
   </si>
   <si>
     <t xml:space="preserve">Lugar de residencia </t>
@@ -216,7 +224,7 @@
     <t>Distintivo y/o nombre comercial del concesionario responsable de publicar la campaña o comunicación</t>
   </si>
   <si>
-    <t>Descripción breve de las razones que justifican la elección del proveedor</t>
+    <t>Descripción breve de las razones que justifican la elección del/la proveedor/a (Redactada con perspectiva de género)</t>
   </si>
   <si>
     <t>Monto total del tiempo de Estado o tiempo fiscal consumidos</t>
@@ -250,12 +258,15 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
+    <t>2023</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
+    <t>Este dato no se requiere para este periodo, de conformidad con las últimas modificaciones a los Lineamientos Técnicos Generales, aprobadas por el Pleno del Consejo Nacional del Sistema Nacional de Transparencia.</t>
+  </si>
+  <si>
     <t>Preparatoria</t>
   </si>
   <si>
@@ -265,34 +276,25 @@
     <t>Departamento de Información y Relaciones Públicas del Colegio de Bachilleres del Estado de Tlaxcala</t>
   </si>
   <si>
-    <t>B52FE8F18CEDE12FFB73EFD752E4BC81</t>
-  </si>
-  <si>
-    <t>01/07/2022</t>
-  </si>
-  <si>
-    <t>30/09/2022</t>
-  </si>
-  <si>
-    <t>4597807</t>
-  </si>
-  <si>
-    <t>17/10/2022</t>
-  </si>
-  <si>
-    <t>Durante el periodo 01 de julio de 2022 al 30 de septiembre de 2022, el Colegio de Bachilleres del Estado de Tlaxcala no tiene inherencia en la utilización de Tiempos Oficiales por lo que hago mención de dos mensajes aclaratorios e informativos: Menasje 1:"La publicación y actualización de la información relativa a la utilización de los Tiempos oficiales está a cargo de la Dirección General de Radio, Televisión y Cinematografía de la Secretaría de Gabernación." Mensaje 2:" La publicación y actualización de la información relativa a la utilización de los Tiempos oficiales esta a cargo del Instituto Nacional Electoral." Por lo que no se genera información alguna.</t>
-  </si>
-  <si>
-    <t>4289428</t>
-  </si>
-  <si>
-    <t>3122340</t>
-  </si>
-  <si>
-    <t>2816098</t>
-  </si>
-  <si>
-    <t>2644462</t>
+    <t>9599DAED267DFBFC1B5A274DE5D358B6</t>
+  </si>
+  <si>
+    <t>01/07/2023</t>
+  </si>
+  <si>
+    <t>30/09/2023</t>
+  </si>
+  <si>
+    <t>8260957</t>
+  </si>
+  <si>
+    <t>03/07/2023</t>
+  </si>
+  <si>
+    <t>11/10/2023</t>
+  </si>
+  <si>
+    <t>Durante el periodo 01 de julio de 2023 al 30 de septiembre de 2023, el Colegio de Bachilleres del Estado de Tlaxcala no tiene inherencia en la utilización de Tiempos Oficiales por lo que hago mención de dos mensajes aclaratorios e informativos: Menasje 1:"La publicación y actualización de la información relativa a la utilización de los Tiempos oficiales está a cargo de la Dirección General de Radio, Televisión y Cinematografía de la Secretaría de Gabernación." Mensaje 2:" La publicación y actualización de la información relativa a la utilización de los Tiempos oficiales esta a cargo del Instituto Nacional Electoral." Por lo que no se genera información alguna.</t>
   </si>
   <si>
     <t>Tiempo de estado</t>
@@ -355,6 +357,15 @@
     <t>Femenino y masculino</t>
   </si>
   <si>
+    <t>Mujer</t>
+  </si>
+  <si>
+    <t>Hombre</t>
+  </si>
+  <si>
+    <t>Mujeres y Hombres</t>
+  </si>
+  <si>
     <t>6</t>
   </si>
   <si>
@@ -377,27 +388,6 @@
   </si>
   <si>
     <t xml:space="preserve">Presupuesto ejercido al periodo reportado de cada partida </t>
-  </si>
-  <si>
-    <t>40D5252ED2749727E0CD7FA45943FEDD</t>
-  </si>
-  <si>
-    <t>Ver nota</t>
-  </si>
-  <si>
-    <t>7708F73158F3CAE24A002A097DE33713</t>
-  </si>
-  <si>
-    <t>613CAFD2F38DE453954367206E5B792C</t>
-  </si>
-  <si>
-    <t>7526AFAFFBF6C22672C718A2EF3BC581</t>
-  </si>
-  <si>
-    <t>Ver Nota</t>
-  </si>
-  <si>
-    <t>0</t>
   </si>
 </sst>
 </file>
@@ -793,10 +783,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AE8"/>
+  <dimension ref="A1:AF8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="35.7109375" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="36.28515625" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -804,37 +794,37 @@
     <col min="6" max="6" width="13.5703125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="29.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="79.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="52.28515625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="62.85546875" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="77.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="27.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="85" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="87.140625" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="62" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="52" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="75.7109375" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="44.28515625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="46.42578125" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="46.5703125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="86" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="255" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="181.85546875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="19.5703125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="85" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="87.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="99.140625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="52" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="75.7109375" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="44.28515625" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="46.42578125" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="46.5703125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="86" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="255" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>1</v>
       </c>
@@ -851,7 +841,7 @@
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>4</v>
       </c>
@@ -866,7 +856,7 @@
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
     </row>
-    <row r="4" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>6</v>
       </c>
@@ -907,58 +897,61 @@
         <v>8</v>
       </c>
       <c r="O4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="P4" t="s">
         <v>9</v>
       </c>
       <c r="Q4" t="s">
+        <v>9</v>
+      </c>
+      <c r="R4" t="s">
         <v>6</v>
       </c>
-      <c r="R4" t="s">
+      <c r="S4" t="s">
         <v>9</v>
-      </c>
-      <c r="S4" t="s">
-        <v>6</v>
       </c>
       <c r="T4" t="s">
         <v>6</v>
       </c>
       <c r="U4" t="s">
+        <v>6</v>
+      </c>
+      <c r="V4" t="s">
         <v>9</v>
-      </c>
-      <c r="V4" t="s">
-        <v>6</v>
       </c>
       <c r="W4" t="s">
         <v>6</v>
       </c>
       <c r="X4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y4" t="s">
         <v>7</v>
       </c>
       <c r="Z4" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA4" t="s">
         <v>10</v>
       </c>
-      <c r="AA4" t="s">
+      <c r="AB4" t="s">
         <v>6</v>
       </c>
-      <c r="AB4" t="s">
+      <c r="AC4" t="s">
         <v>9</v>
       </c>
-      <c r="AC4" t="s">
+      <c r="AD4" t="s">
         <v>7</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AE4" t="s">
         <v>11</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AF4" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:31" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:32" hidden="1" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
         <v>13</v>
       </c>
@@ -1049,10 +1042,13 @@
       <c r="AE5" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
@@ -1084,197 +1080,204 @@
       <c r="AC6" s="5"/>
       <c r="AD6" s="5"/>
       <c r="AE6" s="5"/>
-    </row>
-    <row r="7" spans="1:31" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="AF6" s="5"/>
+    </row>
+    <row r="7" spans="1:32" ht="26.25" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="V7" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="X7" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="Y7" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="Z7" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AA7" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AB7" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AC7" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AD7" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AE7" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>74</v>
+      </c>
+      <c r="AF7" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C8" s="3" t="s">
+      <c r="R8" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="S8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="T8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="U8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="W8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="X8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA8" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="AB8" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="AC8" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="N8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="O8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q8" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="R8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="S8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="T8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="U8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="V8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="W8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="X8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="Y8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="Z8" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="AA8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="AB8" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="AC8" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="AD8" s="3" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="AE8" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
+      </c>
+      <c r="AF8" s="3" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A6:AE6"/>
+    <mergeCell ref="A6:AF6"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="D2:F2"/>
     <mergeCell ref="G2:I2"/>
@@ -1282,18 +1285,21 @@
     <mergeCell ref="D3:F3"/>
     <mergeCell ref="G3:I3"/>
   </mergeCells>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F8:F196">
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="F8:F199">
       <formula1>Hidden_15</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G8:G196">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="G8:G199">
       <formula1>Hidden_26</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L8:L196">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="L8:L199">
       <formula1>Hidden_311</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="N8:N196">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="N8:N199">
       <formula1>Hidden_413</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="O8:O199">
+      <formula1>Hidden_514</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1442,11 +1448,34 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="29.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="45.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="62.5703125" bestFit="1" customWidth="1"/>
@@ -1457,104 +1486,36 @@
         <v>9</v>
       </c>
       <c r="D1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E1" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D2" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="E2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B5" s="3" t="s">
         <v>119</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>123</v>
       </c>
     </row>
   </sheetData>
